--- a/Companies House CSV Data Dictionary.xlsx
+++ b/Companies House CSV Data Dictionary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://itservicemanagementcqcorg-my.sharepoint.com/personal/sam_grafton-waters_cqc_org_uk/Documents/Documents/Data Science Related Work/Companies_House_Retrieval/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/SamWaters/Documents/Data Science/Companies_House_Retrieval/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{C7233BD4-6F9C-4874-8AA3-494D8219E3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A98DEB7-E1EC-40B1-94F1-81E4DF1B1702}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C1A07D-5331-FB4A-B18B-F7033DB19A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="810" xr2:uid="{A5807A93-8B6F-4F0E-A884-EFB3F9B68D98}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="15500" tabRatio="810" activeTab="4" xr2:uid="{A5807A93-8B6F-4F0E-A884-EFB3F9B68D98}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="308">
   <si>
     <t>Company Name</t>
   </si>
@@ -71,12 +71,6 @@
     <t>Registered Office in Dispute</t>
   </si>
   <si>
-    <t>Last Accounts Period End On</t>
-  </si>
-  <si>
-    <t>Last Accounts Period Start On</t>
-  </si>
-  <si>
     <t>Accounts Next Due</t>
   </si>
   <si>
@@ -132,12 +126,6 @@
   </si>
   <si>
     <t>Flags whether the organisation has any charges. Note - use the Charges table for a more reliable dataset</t>
-  </si>
-  <si>
-    <t>Date the timeframe for the last accounts ended - check match in finance tables</t>
-  </si>
-  <si>
-    <t>Date the timeframe for the last accounts started - check match in finance tables</t>
   </si>
   <si>
     <t>Date the next set of accounts are due on</t>
@@ -1141,6 +1129,9 @@
   </si>
   <si>
     <t>The date shown on the Company House website next to the blance sheet link</t>
+  </si>
+  <si>
+    <t>Charge Code</t>
   </si>
 </sst>
 </file>
@@ -1576,7 +1567,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1585,9 +1576,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1708,7 +1696,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2055,187 +2042,187 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="B3:I15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="29.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="104.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="50.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="104.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-    </row>
-    <row r="4" spans="2:9" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="51"/>
-      <c r="C4" s="57" t="s">
+    <row r="3" spans="2:9" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+    </row>
+    <row r="4" spans="2:9" ht="28" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="50"/>
+      <c r="C4" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="72" t="s">
+        <v>229</v>
+      </c>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+    </row>
+    <row r="5" spans="2:9" ht="22" x14ac:dyDescent="0.3">
+      <c r="B5" s="50"/>
+      <c r="C5" s="59" t="s">
+        <v>217</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>233</v>
+      </c>
+      <c r="E5" s="52"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+    </row>
+    <row r="6" spans="2:9" ht="22" x14ac:dyDescent="0.3">
+      <c r="B6" s="50"/>
+      <c r="C6" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="D6" s="51" t="s">
+        <v>225</v>
+      </c>
+      <c r="E6" s="53"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+    </row>
+    <row r="7" spans="2:9" ht="22" x14ac:dyDescent="0.3">
+      <c r="B7" s="50"/>
+      <c r="C7" s="60" t="s">
+        <v>219</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>226</v>
+      </c>
+      <c r="E7" s="53"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+    </row>
+    <row r="8" spans="2:9" ht="22" x14ac:dyDescent="0.3">
+      <c r="B8" s="50"/>
+      <c r="C8" s="60" t="s">
         <v>220</v>
       </c>
-      <c r="D4" s="58" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="74" t="s">
-        <v>233</v>
-      </c>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-    </row>
-    <row r="5" spans="2:9" ht="21" x14ac:dyDescent="0.4">
-      <c r="B5" s="51"/>
-      <c r="C5" s="60" t="s">
+      <c r="D8" s="51" t="s">
+        <v>232</v>
+      </c>
+      <c r="E8" s="53"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+    </row>
+    <row r="9" spans="2:9" ht="22" x14ac:dyDescent="0.3">
+      <c r="B9" s="50"/>
+      <c r="C9" s="60" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="59" t="s">
-        <v>237</v>
-      </c>
-      <c r="E5" s="53"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-    </row>
-    <row r="6" spans="2:9" ht="21" x14ac:dyDescent="0.4">
-      <c r="B6" s="51"/>
-      <c r="C6" s="61" t="s">
+      <c r="D9" s="51" t="s">
+        <v>227</v>
+      </c>
+      <c r="E9" s="53"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+    </row>
+    <row r="10" spans="2:9" ht="22" x14ac:dyDescent="0.3">
+      <c r="B10" s="50"/>
+      <c r="C10" s="61" t="s">
         <v>222</v>
       </c>
-      <c r="D6" s="52" t="s">
-        <v>229</v>
-      </c>
-      <c r="E6" s="54"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-    </row>
-    <row r="7" spans="2:9" ht="21" x14ac:dyDescent="0.4">
-      <c r="B7" s="51"/>
-      <c r="C7" s="61" t="s">
+      <c r="D10" s="51" t="s">
+        <v>230</v>
+      </c>
+      <c r="E10" s="53"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+    </row>
+    <row r="11" spans="2:9" ht="22" x14ac:dyDescent="0.3">
+      <c r="B11" s="50"/>
+      <c r="C11" s="61" t="s">
+        <v>224</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>231</v>
+      </c>
+      <c r="E11" s="53"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+    </row>
+    <row r="12" spans="2:9" ht="22" x14ac:dyDescent="0.3">
+      <c r="B12" s="50"/>
+      <c r="C12" s="64" t="s">
         <v>223</v>
       </c>
-      <c r="D7" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="E7" s="54"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-    </row>
-    <row r="8" spans="2:9" ht="21" x14ac:dyDescent="0.4">
-      <c r="B8" s="51"/>
-      <c r="C8" s="61" t="s">
-        <v>224</v>
-      </c>
-      <c r="D8" s="52" t="s">
-        <v>236</v>
-      </c>
-      <c r="E8" s="54"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-    </row>
-    <row r="9" spans="2:9" ht="21" x14ac:dyDescent="0.4">
-      <c r="B9" s="51"/>
-      <c r="C9" s="61" t="s">
-        <v>225</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>231</v>
-      </c>
-      <c r="E9" s="54"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-    </row>
-    <row r="10" spans="2:9" ht="21" x14ac:dyDescent="0.4">
-      <c r="B10" s="51"/>
-      <c r="C10" s="62" t="s">
-        <v>226</v>
-      </c>
-      <c r="D10" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="E10" s="54"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-    </row>
-    <row r="11" spans="2:9" ht="21" x14ac:dyDescent="0.4">
-      <c r="B11" s="51"/>
-      <c r="C11" s="62" t="s">
+      <c r="D12" s="65" t="s">
         <v>228</v>
       </c>
-      <c r="D11" s="52" t="s">
-        <v>235</v>
-      </c>
-      <c r="E11" s="54"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-    </row>
-    <row r="12" spans="2:9" ht="21" x14ac:dyDescent="0.4">
-      <c r="B12" s="51"/>
-      <c r="C12" s="65" t="s">
-        <v>227</v>
-      </c>
-      <c r="D12" s="66" t="s">
-        <v>232</v>
-      </c>
-      <c r="E12" s="67"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-    </row>
-    <row r="13" spans="2:9" ht="21" x14ac:dyDescent="0.4">
-      <c r="B13" s="51"/>
-      <c r="C13" s="62" t="s">
+      <c r="E12" s="66"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+    </row>
+    <row r="13" spans="2:9" ht="22" x14ac:dyDescent="0.3">
+      <c r="B13" s="50"/>
+      <c r="C13" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="E13" s="53"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+    </row>
+    <row r="14" spans="2:9" ht="22" x14ac:dyDescent="0.3">
+      <c r="B14" s="50"/>
+      <c r="C14" s="61" t="s">
+        <v>277</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>279</v>
+      </c>
+      <c r="E14" s="53"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
+    </row>
+    <row r="15" spans="2:9" ht="23" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C15" s="62" t="s">
+        <v>278</v>
+      </c>
+      <c r="D15" s="54" t="s">
         <v>280</v>
       </c>
-      <c r="D13" s="52" t="s">
-        <v>285</v>
-      </c>
-      <c r="E13" s="54"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-    </row>
-    <row r="14" spans="2:9" ht="21" x14ac:dyDescent="0.4">
-      <c r="B14" s="51"/>
-      <c r="C14" s="62" t="s">
-        <v>281</v>
-      </c>
-      <c r="D14" s="52" t="s">
-        <v>283</v>
-      </c>
-      <c r="E14" s="54"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-    </row>
-    <row r="15" spans="2:9" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C15" s="63" t="s">
-        <v>282</v>
-      </c>
-      <c r="D15" s="55" t="s">
-        <v>284</v>
-      </c>
-      <c r="E15" s="56"/>
+      <c r="E15" s="55"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -2259,378 +2246,378 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{198F9211-C5A1-4870-814E-D0423CA04E83}">
   <dimension ref="B2:E32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="75.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="61.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="75.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="21" t="s">
+    <row r="2" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="18" t="s">
+    </row>
+    <row r="4" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="48" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E5" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B8" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E8" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B9" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E11" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E12" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E13" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="E14" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B18" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="E18" s="48" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="22" t="s">
+      <c r="D19" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="E19" s="7">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B20" s="39" t="s">
+        <v>240</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B21" s="39" t="s">
+        <v>241</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="E21" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="49" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E5" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="C22" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="63" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B26" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="E26" s="29" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B27" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="E27" s="7">
+        <v>45333</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B28" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B29" s="39" t="s">
+        <v>240</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B30" s="39" t="s">
+        <v>241</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="E30" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B31" s="39" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E7" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E8" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E11" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E12" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E13" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="E14" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="2:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="18" t="s">
+      <c r="C31" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="E18" s="49" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B19" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="E19" s="8">
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B21" s="40" t="s">
-        <v>245</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>272</v>
-      </c>
-      <c r="E21" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" s="64" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="2:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B26" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>276</v>
-      </c>
-      <c r="E26" s="30" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B27" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27" s="31" t="s">
+      <c r="D32" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="E27" s="8">
-        <v>45333</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="C28" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="31" t="s">
-        <v>274</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="C29" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B30" s="40" t="s">
-        <v>245</v>
-      </c>
-      <c r="C30" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="31" t="s">
-        <v>272</v>
-      </c>
-      <c r="E30" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B31" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="E32" s="35">
+      <c r="E32" s="34">
         <v>45334</v>
       </c>
     </row>
@@ -2645,441 +2632,441 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="B2:E37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="34.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="98.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="24" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-    </row>
-    <row r="3" spans="2:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="15" t="s">
+    <row r="2" spans="2:5" ht="25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+    </row>
+    <row r="3" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="16" t="s">
+    </row>
+    <row r="4" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="69" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="71" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C5" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="71" t="s">
+      <c r="D5" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="E5" s="40">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>306</v>
+      </c>
+      <c r="E6" s="40">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="47" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="E7" s="40">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B8" s="47" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="E8" s="40">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B9" s="47" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="E9" s="49">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="E10" s="40">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="E11" s="40">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="E12" s="40">
+        <v>12441</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="E13" s="40">
+        <v>31441</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="40">
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B15" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="E15" s="40">
+        <v>14521</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B16" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="E16" s="40">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B17" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="E17" s="40">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B18" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="E18" s="40">
+        <v>10331</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E19" s="40">
+        <v>11922</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B20" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" s="40">
+        <v>453011</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B21" s="47" t="s">
+        <v>290</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="E21" s="40">
+        <v>478221</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B22" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="24"/>
+    </row>
+    <row r="23" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B23" s="47" t="s">
+        <v>292</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="24"/>
+    </row>
+    <row r="24" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B24" s="47" t="s">
+        <v>293</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="E24" s="40">
+        <v>4309</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B25" s="47" t="s">
+        <v>294</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E25" s="40">
+        <v>5612</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B26" s="47" t="s">
+        <v>295</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="24"/>
+    </row>
+    <row r="27" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B27" s="47" t="s">
+        <v>296</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="24"/>
+    </row>
+    <row r="28" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B28" s="47" t="s">
+        <v>297</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="24"/>
+    </row>
+    <row r="29" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B29" s="47" t="s">
+        <v>298</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="24"/>
+    </row>
+    <row r="30" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B30" s="47" t="s">
+        <v>299</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" s="40">
+        <v>5002</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="B31" s="47" t="s">
+        <v>300</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="E31" s="40">
+        <v>4291</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="B32" s="47" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="72" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="73" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="48" t="s">
-        <v>286</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>309</v>
-      </c>
-      <c r="E5" s="41">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>310</v>
-      </c>
-      <c r="E6" s="41">
-        <v>46117</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="48" t="s">
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="24"/>
+    </row>
+    <row r="33" spans="2:5" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="B33" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="31" t="s">
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="24"/>
+    </row>
+    <row r="34" spans="2:5" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="B34" s="47" t="s">
+        <v>301</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="E34" s="40">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" s="1" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="E7" s="41">
-        <v>45748</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="48" t="s">
-        <v>196</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>203</v>
-      </c>
-      <c r="E8" s="41">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="48" t="s">
-        <v>197</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="E9" s="50">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="48" t="s">
-        <v>200</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="E10" s="41">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>217</v>
-      </c>
-      <c r="E11" s="41">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="48" t="s">
-        <v>239</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="E12" s="41">
-        <v>12441</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="48" t="s">
-        <v>238</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="E13" s="41">
-        <v>31441</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="48" t="s">
-        <v>287</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="E14" s="41">
-        <v>15500</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="48" t="s">
-        <v>288</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="E15" s="41">
-        <v>14521</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="48" t="s">
-        <v>289</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="E16" s="69">
-        <v>2564</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="48" t="s">
-        <v>290</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>308</v>
-      </c>
-      <c r="E17" s="69">
-        <v>2145</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="48" t="s">
-        <v>291</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="E18" s="41">
-        <v>10331</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B19" s="48" t="s">
-        <v>292</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>213</v>
-      </c>
-      <c r="E19" s="41">
-        <v>11922</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="48" t="s">
-        <v>293</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="E20" s="41">
-        <v>453011</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B21" s="48" t="s">
-        <v>294</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="E21" s="41">
-        <v>478221</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B22" s="48" t="s">
-        <v>295</v>
-      </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="25"/>
-    </row>
-    <row r="23" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B23" s="48" t="s">
-        <v>296</v>
-      </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="25"/>
-    </row>
-    <row r="24" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B24" s="48" t="s">
-        <v>297</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="E24" s="41">
-        <v>4309</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B25" s="48" t="s">
-        <v>298</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="E25" s="41">
-        <v>5612</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B26" s="48" t="s">
-        <v>299</v>
-      </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="25"/>
-    </row>
-    <row r="27" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B27" s="48" t="s">
-        <v>300</v>
-      </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="25"/>
-    </row>
-    <row r="28" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="48" t="s">
-        <v>301</v>
-      </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="25"/>
-    </row>
-    <row r="29" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="48" t="s">
-        <v>302</v>
-      </c>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="25"/>
-    </row>
-    <row r="30" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B30" s="48" t="s">
-        <v>303</v>
-      </c>
-      <c r="C30" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D30" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="E30" s="41">
-        <v>5002</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B31" s="48" t="s">
-        <v>304</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="D31" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="E31" s="41">
-        <v>4291</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B32" s="48" t="s">
-        <v>198</v>
-      </c>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="25"/>
-    </row>
-    <row r="33" spans="2:5" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B33" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="25"/>
-    </row>
-    <row r="34" spans="2:5" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B34" s="48" t="s">
-        <v>305</v>
-      </c>
-      <c r="C34" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" s="31" t="s">
-        <v>205</v>
-      </c>
-      <c r="E34" s="41">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" s="1" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="70" t="s">
-        <v>306</v>
-      </c>
-      <c r="C35" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" s="34" t="s">
-        <v>206</v>
-      </c>
-      <c r="E35" s="47">
+      <c r="E35" s="46">
         <v>2024</v>
       </c>
     </row>
-    <row r="36" spans="2:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B36"/>
       <c r="C36"/>
       <c r="D36"/>
       <c r="E36"/>
     </row>
-    <row r="37" spans="2:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -3093,215 +3080,205 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55FEB228-2F3F-4364-B664-9DB2D9335A0A}">
-  <dimension ref="B2:E17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:E17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="18.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="31.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="95.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="95.83203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="6" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="15" t="s">
+    <row r="2" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="16" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4"/>
+      <c r="B4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5"/>
+      <c r="B5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6"/>
+      <c r="B6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7"/>
+      <c r="B7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="5" t="s">
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="7">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8"/>
+      <c r="B8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9"/>
+      <c r="B9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="D9" s="3"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10"/>
+      <c r="B10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D10" s="3"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11"/>
+      <c r="B11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="7">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12"/>
+      <c r="B12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="8">
+      <c r="D12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13"/>
+      <c r="B13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14"/>
+      <c r="B14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="7">
         <v>45292</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="6" t="b">
+    <row r="15" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15"/>
+      <c r="B15" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="8">
-        <v>45292</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="8">
-        <v>45292</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="8">
-        <v>45292</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="11" t="b">
-        <v>1</v>
-      </c>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3313,247 +3290,258 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15EF5264-368E-4981-A103-255E69D1470C}">
-  <dimension ref="B2:E20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:E21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="91" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="64.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="64.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="21" t="s">
+    <row r="2" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="18" t="s">
+    </row>
+    <row r="4" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="17"/>
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="22" t="s">
+      <c r="D7" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="7">
+        <v>41961</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B8" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="7">
+        <v>41961</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="12" t="s">
+      <c r="C9" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C10" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="D11" s="32"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="32"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="32"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="32"/>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B15" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="35">
+        <v>9284483</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B16" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B17" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="7">
         <v>41961</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="8">
-        <v>41961</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="31" t="s">
+    <row r="18" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B18" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="33"/>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="12" t="s">
+    </row>
+    <row r="19" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="C19" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="36">
-        <v>9284483</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="12" t="s">
+    </row>
+    <row r="20" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B20" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="8">
-        <v>41961</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="31" t="s">
+      <c r="C21" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B19" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="35">
+      <c r="E21" s="34">
         <v>41961</v>
       </c>
     </row>
@@ -3568,278 +3556,278 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="B2:E21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="72" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="15" t="s">
+    <row r="2" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="38" t="s">
+    </row>
+    <row r="4" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="30">
+      <c r="C4" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="29">
         <v>39285463</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="40" t="s">
+    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E6" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B8" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B9" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="E10" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="E14" s="24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B15" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="C5" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="E6" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="40" t="s">
-        <v>147</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="E7" s="25">
+      <c r="C15" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" s="24">
+        <v>0.36599999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B16" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16" s="24">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B17" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" s="24">
+        <v>0.52100000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B18" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E18" s="24">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="E19" s="24">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="40" t="s">
-        <v>148</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E8" s="25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9" s="25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="E10" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="E12" s="25">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="40" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="E13" s="25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="E14" s="25">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15" s="25">
-        <v>0.36599999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="40" t="s">
+    <row r="20" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B20" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="C16" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="D16" s="20" t="s">
+      <c r="C20" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="D20" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="E16" s="25">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="40" t="s">
+      <c r="E20" s="24">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" s="20" t="s">
+      <c r="C21" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="E17" s="25">
-        <v>0.52100000000000002</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="E18" s="25">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B19" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="E19" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="E20" s="25">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="D21" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="E21" s="28">
+      <c r="E21" s="27">
         <v>0.25</v>
       </c>
     </row>
@@ -3851,199 +3839,199 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B0CD4E-929E-4E3B-9423-FF8C0ADE9D7E}">
   <dimension ref="B2:E15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="104.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="104.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="21" t="s">
+    <row r="2" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="18" t="s">
+    </row>
+    <row r="4" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="29">
+        <v>39285463</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="42">
+        <v>90924682245</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B8" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="38" t="s">
+      <c r="D8" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="7">
+        <v>42471</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B9" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="7">
+        <v>46617</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="7">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="C4" s="29" t="s">
+    </row>
+    <row r="13" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="30">
-        <v>39285463</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" s="43">
-        <v>90924682245</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" s="8">
-        <v>42471</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="31" t="s">
+      <c r="D13" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="6" t="b">
+      <c r="E13" s="5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="31" t="s">
+    <row r="14" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="8">
-        <v>46617</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="31" t="s">
+      <c r="E14" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="E11" s="8">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="31" t="s">
+      <c r="E15" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -4054,209 +4042,209 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94A0E5A-AC56-4BD5-BF38-16E9EF37E120}">
   <dimension ref="B2:E16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" customWidth="1"/>
-    <col min="2" max="2" width="36.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="104.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.5546875" customWidth="1"/>
+    <col min="1" max="1" width="15.5" customWidth="1"/>
+    <col min="2" max="2" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="104.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="21" t="s">
+    <row r="2" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="18" t="s">
+    </row>
+    <row r="4" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B8" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="5">
+        <v>39285463</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B9" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="23" t="s">
+      <c r="D11" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="7">
+        <v>42471</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D12" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="7">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="24" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="20" t="s">
+      <c r="E14" s="7">
+        <v>46345</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B15" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="7">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E8" s="6">
-        <v>39285463</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="31" t="s">
+      <c r="D16" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="8">
-        <v>42471</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="E12" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="E13" s="8">
-        <v>46332</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="E14" s="8">
-        <v>46345</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="E15" s="8">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="11" t="b">
+      <c r="E16" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4271,222 +4259,222 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="B2:E17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="37.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="77.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="77.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="21" t="s">
+    <row r="2" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="38" t="s">
+    </row>
+    <row r="4" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="E7" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B8" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="39" t="s">
+      <c r="C8" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="E4" s="30" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="40" t="s">
+      <c r="E8" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B9" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="C5" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="31" t="s">
+      <c r="C9" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="30" t="s">
         <v>181</v>
       </c>
-      <c r="E5" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="40" t="s">
+      <c r="E9" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="C6" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="31" t="s">
+      <c r="C10" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="E6" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="40" t="s">
+      <c r="E10" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="31" t="s">
+      <c r="C11" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E11" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="E13" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="40" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="E8" s="6">
+    <row r="14" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B15" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="E15" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B16" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="E16" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="40" t="s">
-        <v>171</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="E11" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="E12" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="40" t="s">
+    <row r="17" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="C13" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="31" t="s">
+      <c r="C17" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="E13" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="E15" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="E16" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="42" t="s">
-        <v>179</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="E17" s="11">
+      <c r="E17" s="10">
         <v>2</v>
       </c>
     </row>
@@ -4498,180 +4486,180 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86398811-FBB8-4B33-9029-937C755F34A5}">
   <dimension ref="B2:E14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="37.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="91" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="105.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="21" t="s">
+    <row r="2" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="18" t="s">
+    </row>
+    <row r="4" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="29">
+        <v>39285463</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B8" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="29" t="s">
+      <c r="D8" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="7">
+        <v>41961</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B9" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="7">
+        <v>41961</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="30">
-        <v>39285463</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="5" t="s">
+      <c r="D10" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="45" t="s">
-        <v>111</v>
-      </c>
-      <c r="E7" s="46" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="E8" s="8">
-        <v>41961</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9" s="8">
-        <v>41961</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="5" t="s">
+      <c r="C13" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="7">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="E10" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="E13" s="8">
-        <v>46332</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" s="35">
+      <c r="C14" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="34">
         <v>46345</v>
       </c>
     </row>
@@ -4681,14 +4669,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d400e6ca-83e7-4ec8-8dba-73297945a25b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="62c0568a-750b-4e53-9e60-20dd32e5e402">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4921,21 +4907,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d400e6ca-83e7-4ec8-8dba-73297945a25b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="62c0568a-750b-4e53-9e60-20dd32e5e402">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{914EDA56-117D-4F3A-B12C-F495439EC5A7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF42BF03-D490-44FF-857F-8695E90A9225}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d400e6ca-83e7-4ec8-8dba-73297945a25b"/>
-    <ds:schemaRef ds:uri="62c0568a-750b-4e53-9e60-20dd32e5e402"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4960,9 +4945,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF42BF03-D490-44FF-857F-8695E90A9225}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{914EDA56-117D-4F3A-B12C-F495439EC5A7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d400e6ca-83e7-4ec8-8dba-73297945a25b"/>
+    <ds:schemaRef ds:uri="62c0568a-750b-4e53-9e60-20dd32e5e402"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Companies House CSV Data Dictionary.xlsx
+++ b/Companies House CSV Data Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/SamWaters/Documents/Data Science/Companies_House_Retrieval/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A48698-487D-2445-8AD1-070D41A61938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F560CAC-52B8-8F42-B624-8969A589E744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="500" windowWidth="25600" windowHeight="15500" tabRatio="810" xr2:uid="{A5807A93-8B6F-4F0E-A884-EFB3F9B68D98}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="15500" tabRatio="810" xr2:uid="{A5807A93-8B6F-4F0E-A884-EFB3F9B68D98}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="358">
   <si>
     <t>Company Name</t>
   </si>
@@ -97,9 +97,6 @@
     <t>THE GABLES CARE LIMITED</t>
   </si>
   <si>
-    <t>08864916</t>
-  </si>
-  <si>
     <t>active, disolved</t>
   </si>
   <si>
@@ -239,9 +236,6 @@
   </si>
   <si>
     <t>Date the transaction was started</t>
-  </si>
-  <si>
-    <t>Date the transaction was flagged or sent to CH</t>
   </si>
   <si>
     <t>Appointed On</t>
@@ -860,48 +854,12 @@
     <t>Charges_Transactions</t>
   </si>
   <si>
-    <t>Number_Prop_Charges</t>
-  </si>
-  <si>
-    <t>Officers</t>
-  </si>
-  <si>
-    <t>Person other Orgs</t>
-  </si>
-  <si>
-    <t>Significant Control</t>
-  </si>
-  <si>
-    <t>Count Orgs Per Person</t>
-  </si>
-  <si>
-    <t>Table with the overview details about the Company/Organisation</t>
-  </si>
-  <si>
-    <t>Table with details related to charges and transactions</t>
-  </si>
-  <si>
-    <t>Table with details about officers associated with each Company/Organisation</t>
-  </si>
-  <si>
-    <t>Table with details about persons with significant control for each Company/Organisation</t>
-  </si>
-  <si>
     <t>CSV Filename</t>
   </si>
   <si>
-    <t>Table with high level details around which Companies/Organisations each person is associated with</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table showing the count of Companies/Organisations, roles, and statuses each person </t>
-  </si>
-  <si>
     <t>Table with the number and proportions of charges (and types) associated with each organisation</t>
   </si>
   <si>
-    <t>Table with the financial details for each organisation, taking data from within a 12 year period</t>
-  </si>
-  <si>
     <t>Fixed Assets Previous</t>
   </si>
   <si>
@@ -1022,24 +980,9 @@
     <t>Joe Bloggs</t>
   </si>
   <si>
-    <t>Insolvency - Count</t>
-  </si>
-  <si>
-    <t>Insolvency - Dates</t>
-  </si>
-  <si>
-    <t>Insolvency - Practioners</t>
-  </si>
-  <si>
     <t>Dates and process for each insolvency</t>
   </si>
   <si>
-    <t>Practioners/people associated with the Insolvency</t>
-  </si>
-  <si>
-    <t>Counts of number of insolvencies and their different types</t>
-  </si>
-  <si>
     <t>Account Date</t>
   </si>
   <si>
@@ -1151,9 +1094,6 @@
     <t>Flags whether the Acounts data is overdue (i.e. not submitted)</t>
   </si>
   <si>
-    <t>Companies House ID number for company/company</t>
-  </si>
-  <si>
     <t>Date company was created/started</t>
   </si>
   <si>
@@ -1214,19 +1154,167 @@
     <t>FROM ROLE: Number of organisations the person is a 'llp-designated-member'</t>
   </si>
   <si>
-    <t>Count_Insolvency_Details_Date</t>
-  </si>
-  <si>
     <t>Note, given the differnce in companies and the range of different values/options for each table, what is shown in these tables may differ to what you observe when running the code.</t>
+  </si>
+  <si>
+    <t>Date the transaction was flagged or sent to Companies House</t>
+  </si>
+  <si>
+    <t>Does the charge contain a floating charge?</t>
+  </si>
+  <si>
+    <t>Does the charge contain a fixed charge?</t>
+  </si>
+  <si>
+    <t>Does the charge contain a negative pledge?</t>
+  </si>
+  <si>
+    <t>Does the floating charge cover all assets?</t>
+  </si>
+  <si>
+    <t>Specific charge code</t>
+  </si>
+  <si>
+    <t>THIS IS A BREIF DESCRIPTION EXAMPLE</t>
+  </si>
+  <si>
+    <t>[{'name': 'Barclays Bank PLC'}]</t>
+  </si>
+  <si>
+    <t>Who is being paid</t>
+  </si>
+  <si>
+    <t>[{'delivered_on': '2024-02-27', 'filing_type': 'create-charge-with-deed', 'links': {'filing': '/company/11481000/filing-history/MzQxMjU5MjI1OWFkaXF6a2N4'}}]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Details of the transactions. This row is used to create the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Company_Transactions_Table_DATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, below</t>
+    </r>
+  </si>
+  <si>
+    <t>dictionary</t>
+  </si>
+  <si>
+    <t>charge-description</t>
+  </si>
+  <si>
+    <t>type of charge</t>
+  </si>
+  <si>
+    <t>Description of the type of charge</t>
+  </si>
+  <si>
+    <t>Particular type of charge</t>
+  </si>
+  <si>
+    <t>short-particulars</t>
+  </si>
+  <si>
+    <t>create, satisfy</t>
+  </si>
+  <si>
+    <t>MR01, MR04</t>
+  </si>
+  <si>
+    <t>Specific code of the type of transaction</t>
+  </si>
+  <si>
+    <t>Date transaction happened</t>
+  </si>
+  <si>
+    <t>Date logged with Companies House</t>
+  </si>
+  <si>
+    <t>What is happening or being done in the transaction</t>
+  </si>
+  <si>
+    <t>Desription of the transaction</t>
+  </si>
+  <si>
+    <t>Officers_Signif_Control</t>
+  </si>
+  <si>
+    <t>Insolvency</t>
+  </si>
+  <si>
+    <t>Table Description</t>
+  </si>
+  <si>
+    <t>Finance_Data_DATE</t>
+  </si>
+  <si>
+    <t>DATE - Refers to the date the code is ran. This will be included in the output filename</t>
+  </si>
+  <si>
+    <t>Insolvency_Dates_Types_DATE</t>
+  </si>
+  <si>
+    <t>Count of different types and number of insolvencies per company</t>
+  </si>
+  <si>
+    <t>Person and their role when a Company becomes insolvent</t>
+  </si>
+  <si>
+    <t>Table with the financial details for each company</t>
+  </si>
+  <si>
+    <t>Table with the overview details for each company</t>
+  </si>
+  <si>
+    <t>Table with details related to charges for each company</t>
+  </si>
+  <si>
+    <t>Table with details about officers associated with each company</t>
+  </si>
+  <si>
+    <t>Table with details about persons with significant control for each company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table showing the count of companies, roles, and statuses for each person </t>
+  </si>
+  <si>
+    <t>Table with high level details around which different companies each person is associated with</t>
+  </si>
+  <si>
+    <t>Table with the details of transactions</t>
+  </si>
+  <si>
+    <t>Table with details related to both charges and transactions for each Company</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1341,28 +1429,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="27">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1629,45 +1730,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1720,201 +1782,383 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2254,217 +2498,264 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="B3:I19"/>
+  <dimension ref="B3:H21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="104.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="50.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="111" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-    </row>
-    <row r="4" spans="2:9" ht="28" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="45"/>
-      <c r="C4" s="51" t="s">
+    <row r="3" spans="2:8" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+    </row>
+    <row r="4" spans="2:8" ht="28" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>343</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>216</v>
+      </c>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+    </row>
+    <row r="5" spans="2:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="B5" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" s="127" t="s">
+        <v>349</v>
+      </c>
+      <c r="D5" s="133" t="s">
+        <v>344</v>
+      </c>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+    </row>
+    <row r="6" spans="2:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="B6" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="D4" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="67" t="s">
-        <v>227</v>
-      </c>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-    </row>
-    <row r="5" spans="2:9" ht="22" x14ac:dyDescent="0.3">
-      <c r="B5" s="45"/>
-      <c r="C5" s="54" t="s">
+      <c r="C6" s="129" t="s">
+        <v>350</v>
+      </c>
+      <c r="D6" s="128" t="s">
+        <v>299</v>
+      </c>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+    </row>
+    <row r="7" spans="2:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="B7" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="D5" s="53" t="s">
-        <v>231</v>
-      </c>
-      <c r="E5" s="47"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-    </row>
-    <row r="6" spans="2:9" ht="22" x14ac:dyDescent="0.3">
-      <c r="B6" s="45"/>
-      <c r="C6" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>223</v>
-      </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-    </row>
-    <row r="7" spans="2:9" ht="22" x14ac:dyDescent="0.3">
-      <c r="B7" s="45"/>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="129" t="s">
+        <v>351</v>
+      </c>
+      <c r="D7" s="137" t="s">
+        <v>306</v>
+      </c>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+    </row>
+    <row r="8" spans="2:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="B8" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="138" t="s">
+        <v>356</v>
+      </c>
+      <c r="D8" s="137" t="s">
+        <v>307</v>
+      </c>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+    </row>
+    <row r="9" spans="2:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="B9" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" s="138" t="s">
+        <v>357</v>
+      </c>
+      <c r="D9" s="139" t="s">
+        <v>308</v>
+      </c>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+    </row>
+    <row r="10" spans="2:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="B10" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="129" t="s">
         <v>217</v>
       </c>
-      <c r="D7" s="46" t="s">
-        <v>224</v>
-      </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-    </row>
-    <row r="8" spans="2:9" ht="22" x14ac:dyDescent="0.3">
-      <c r="B8" s="45"/>
-      <c r="C8" s="55" t="s">
-        <v>218</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>230</v>
-      </c>
-      <c r="E8" s="48"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-    </row>
-    <row r="9" spans="2:9" ht="22" x14ac:dyDescent="0.3">
-      <c r="B9" s="45"/>
-      <c r="C9" s="55" t="s">
-        <v>219</v>
-      </c>
-      <c r="D9" s="46" t="s">
-        <v>225</v>
-      </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-    </row>
-    <row r="10" spans="2:9" ht="22" x14ac:dyDescent="0.3">
-      <c r="B10" s="45"/>
-      <c r="C10" s="56" t="s">
-        <v>220</v>
-      </c>
-      <c r="D10" s="46" t="s">
-        <v>228</v>
-      </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-    </row>
-    <row r="11" spans="2:9" ht="22" x14ac:dyDescent="0.3">
-      <c r="B11" s="45"/>
-      <c r="C11" s="56" t="s">
-        <v>222</v>
-      </c>
-      <c r="D11" s="46" t="s">
-        <v>229</v>
-      </c>
-      <c r="E11" s="48"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-    </row>
-    <row r="12" spans="2:9" ht="22" x14ac:dyDescent="0.3">
-      <c r="B12" s="45"/>
-      <c r="C12" s="59" t="s">
-        <v>221</v>
-      </c>
-      <c r="D12" s="60" t="s">
-        <v>226</v>
-      </c>
-      <c r="E12" s="61"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-    </row>
-    <row r="13" spans="2:9" ht="22" x14ac:dyDescent="0.3">
-      <c r="B13" s="45"/>
-      <c r="C13" s="56" t="s">
-        <v>272</v>
-      </c>
-      <c r="D13" s="46" t="s">
-        <v>277</v>
-      </c>
-      <c r="E13" s="48"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-    </row>
-    <row r="14" spans="2:9" ht="22" x14ac:dyDescent="0.3">
-      <c r="B14" s="45"/>
-      <c r="C14" s="56" t="s">
-        <v>273</v>
-      </c>
-      <c r="D14" s="46" t="s">
-        <v>275</v>
-      </c>
-      <c r="E14" s="48"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-    </row>
-    <row r="15" spans="2:9" ht="23" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="57" t="s">
-        <v>274</v>
-      </c>
-      <c r="D15" s="49" t="s">
-        <v>276</v>
-      </c>
-      <c r="E15" s="50"/>
-    </row>
-    <row r="17" spans="3:4" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C18" s="94" t="s">
-        <v>337</v>
-      </c>
-      <c r="D18" s="95"/>
-    </row>
-    <row r="19" spans="3:4" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="96"/>
-      <c r="D19" s="97"/>
+      <c r="D10" s="137" t="s">
+        <v>309</v>
+      </c>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+    </row>
+    <row r="11" spans="2:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="B11" s="42" t="s">
+        <v>341</v>
+      </c>
+      <c r="C11" s="129" t="s">
+        <v>352</v>
+      </c>
+      <c r="D11" s="137" t="s">
+        <v>310</v>
+      </c>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+    </row>
+    <row r="12" spans="2:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="B12" s="42" t="s">
+        <v>341</v>
+      </c>
+      <c r="C12" s="129" t="s">
+        <v>353</v>
+      </c>
+      <c r="D12" s="130" t="s">
+        <v>311</v>
+      </c>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+    </row>
+    <row r="13" spans="2:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="B13" s="42" t="s">
+        <v>341</v>
+      </c>
+      <c r="C13" s="129" t="s">
+        <v>354</v>
+      </c>
+      <c r="D13" s="130" t="s">
+        <v>313</v>
+      </c>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+    </row>
+    <row r="14" spans="2:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="B14" s="42" t="s">
+        <v>341</v>
+      </c>
+      <c r="C14" s="129" t="s">
+        <v>355</v>
+      </c>
+      <c r="D14" s="130" t="s">
+        <v>314</v>
+      </c>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+    </row>
+    <row r="15" spans="2:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="B15" s="42" t="s">
+        <v>342</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>347</v>
+      </c>
+      <c r="D15" s="130" t="s">
+        <v>300</v>
+      </c>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+    </row>
+    <row r="16" spans="2:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="B16" s="42" t="s">
+        <v>342</v>
+      </c>
+      <c r="C16" s="129" t="s">
+        <v>258</v>
+      </c>
+      <c r="D16" s="136" t="s">
+        <v>346</v>
+      </c>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+    </row>
+    <row r="17" spans="2:4" ht="23" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="43" t="s">
+        <v>342</v>
+      </c>
+      <c r="C17" s="131" t="s">
+        <v>348</v>
+      </c>
+      <c r="D17" s="132" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="69" t="s">
+        <v>316</v>
+      </c>
+      <c r="C20" s="70"/>
+      <c r="D20" s="134" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="71"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="135"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C18:D19"/>
+  <mergeCells count="2">
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="D20:D21"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C5" location="Finance!A1" display="Finance!A1" xr:uid="{E8D45879-7F7B-45D8-80DD-72C915C1C996}"/>
-    <hyperlink ref="C6" location="Overview!A1" display="Overview!A1" xr:uid="{2A2A4FEC-1CEC-4D1B-AB9C-37749B1CF650}"/>
-    <hyperlink ref="C7" location="Charges_Transactions!A1" display="Charges_Transactions!A1" xr:uid="{A681C102-9849-417B-B5AE-3F504E544302}"/>
-    <hyperlink ref="C8" location="Number_Prop_Charges!A1" display="Number_Prop_Charges!A1" xr:uid="{794F2108-5025-413E-9D03-31F14B2E12FA}"/>
-    <hyperlink ref="C9" location="Officers!A1" display="Officers!A1" xr:uid="{7D3C022B-A058-4462-B9F3-D223FA97A1CD}"/>
-    <hyperlink ref="C10" location="'Person other Orgs'!A1" display="'Person other Orgs'!A1" xr:uid="{B3C98453-ED21-4489-97C0-9E5A47E56B82}"/>
-    <hyperlink ref="C12" location="'Significant Control'!A1" display="'Significant Control'!A1" xr:uid="{DF5E77DC-741E-4FC6-BA7D-E2167277914F}"/>
-    <hyperlink ref="C11" location="'Count Orgs Per Person'!A1" display="'Count Orgs Per Person'!A1" xr:uid="{9D09FA53-0246-4109-9878-58E4C3DD15AB}"/>
-    <hyperlink ref="C13" location="Insolvency!A1" display="Insolvency - Count" xr:uid="{29203C5A-5108-4BDD-A696-1BDEF814CE58}"/>
-    <hyperlink ref="C14" location="Insolvency!A1" display="Insolvency - Dates" xr:uid="{E4F4CE38-6009-4CBA-A368-0C3FC97DB1AD}"/>
-    <hyperlink ref="C15" location="Insolvency!A1" display="Insolvency - Practioners" xr:uid="{D324DEC2-7D95-4B3D-BB1A-2AFED815A67E}"/>
+    <hyperlink ref="B5" location="Finance!A1" display="Finance!A1" xr:uid="{E8D45879-7F7B-45D8-80DD-72C915C1C996}"/>
+    <hyperlink ref="B6" location="Overview!A1" display="Overview!A1" xr:uid="{2A2A4FEC-1CEC-4D1B-AB9C-37749B1CF650}"/>
+    <hyperlink ref="B7" location="Charges_Transactions!A1" display="Charges_Transactions!A1" xr:uid="{A681C102-9849-417B-B5AE-3F504E544302}"/>
+    <hyperlink ref="B11" location="Officers_Signif_Control!A1" display="Officers_Signif_Control" xr:uid="{9D09FA53-0246-4109-9878-58E4C3DD15AB}"/>
+    <hyperlink ref="B17" location="Insolvency!A1" display="Insolvency - Practioners" xr:uid="{D324DEC2-7D95-4B3D-BB1A-2AFED815A67E}"/>
+    <hyperlink ref="B8" location="Charges_Transactions!A1" display="Charges_Transactions!A1" xr:uid="{66DD50EF-41E5-F749-ADF6-55248AFC426E}"/>
+    <hyperlink ref="B9" location="Charges_Transactions!A1" display="Charges_Transactions!A1" xr:uid="{29B4FF15-CCD9-584A-A302-50B660AA5F68}"/>
+    <hyperlink ref="B10" location="Charges_Transactions!A1" display="Charges_Transactions!A1" xr:uid="{A389D7B3-7042-A045-AEBA-66028B84F3A7}"/>
+    <hyperlink ref="B12" location="Officers_Signif_Control!A1" display="Officers_Signif_Control" xr:uid="{B0777F75-565E-7F4E-A49A-8F52957104DC}"/>
+    <hyperlink ref="B13" location="Officers_Signif_Control!A1" display="Officers_Signif_Control" xr:uid="{4A2E110B-324B-704A-AE81-477B6336162B}"/>
+    <hyperlink ref="B14" location="Officers_Signif_Control!A1" display="Officers_Signif_Control" xr:uid="{1BA5F3C5-B04A-3046-ACFE-47BC3F9212AF}"/>
+    <hyperlink ref="B15" location="Insolvency!A1" display="Insolvency - Practioners" xr:uid="{A73302C8-DD86-6D47-B58D-40E2F3AFE9D7}"/>
+    <hyperlink ref="B16" location="Insolvency!A1" display="Insolvency - Practioners" xr:uid="{4B9FD5B7-963C-FC44-B9B1-5679439C73B9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2483,17 +2774,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
+      <c r="B2" s="126" t="s">
+        <v>344</v>
+      </c>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
     </row>
     <row r="3" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>13</v>
@@ -2503,423 +2796,423 @@
       </c>
     </row>
     <row r="4" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B4" s="64" t="s">
+      <c r="B4" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="48">
+        <v>12345678</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="E5" s="31">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="E6" s="31">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="E7" s="52">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B8" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="C4" s="65" t="s">
+      <c r="C8" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="66" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B5" s="43" t="s">
-        <v>278</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="E5" s="36">
+      <c r="D8" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="E8" s="52">
         <v>46112</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B6" s="43" t="s">
+    <row r="9" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B9" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>196</v>
+      </c>
+      <c r="E9" s="53">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="E6" s="36">
-        <v>46117</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7" s="68" t="s">
-        <v>189</v>
-      </c>
-      <c r="C7" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="69" t="s">
-        <v>196</v>
-      </c>
-      <c r="E7" s="70">
-        <v>45748</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B8" s="68" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="69" t="s">
-        <v>197</v>
-      </c>
-      <c r="E8" s="70">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B9" s="68" t="s">
-        <v>191</v>
-      </c>
-      <c r="C9" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="69" t="s">
-        <v>198</v>
-      </c>
-      <c r="E9" s="71">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B10" s="68" t="s">
-        <v>194</v>
-      </c>
-      <c r="C10" s="69" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="69" t="s">
+      <c r="D10" s="51" t="s">
+        <v>208</v>
+      </c>
+      <c r="E10" s="52">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="50" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>209</v>
+      </c>
+      <c r="E11" s="52">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>220</v>
+      </c>
+      <c r="E12" s="52">
+        <v>12441</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="50" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>221</v>
+      </c>
+      <c r="E13" s="52">
+        <v>31441</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" s="50" t="s">
+        <v>260</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="E14" s="52">
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B15" s="50" t="s">
+        <v>261</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="52">
+        <v>14521</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B16" s="50" t="s">
+        <v>262</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D16" s="51" t="s">
+        <v>276</v>
+      </c>
+      <c r="E16" s="52">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B17" s="50" t="s">
+        <v>263</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="E17" s="52">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B18" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D18" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="E18" s="52">
+        <v>10331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" s="50" t="s">
+        <v>265</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>205</v>
+      </c>
+      <c r="E19" s="52">
+        <v>11922</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B20" s="50" t="s">
+        <v>266</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="E20" s="52">
+        <v>453011</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B21" s="50" t="s">
+        <v>267</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="E21" s="52">
+        <v>478221</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B22" s="50" t="s">
+        <v>268</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D22" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="E22" s="52">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B23" s="50" t="s">
+        <v>269</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="E23" s="51">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B24" s="50" t="s">
+        <v>270</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>202</v>
+      </c>
+      <c r="E24" s="51">
+        <v>4309</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B25" s="50" t="s">
+        <v>271</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>203</v>
+      </c>
+      <c r="E25" s="51">
+        <v>5612</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B26" s="50" t="s">
+        <v>287</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>291</v>
+      </c>
+      <c r="E26" s="51">
+        <v>7127</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B27" s="50" t="s">
+        <v>288</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>292</v>
+      </c>
+      <c r="E27" s="51">
+        <v>2727</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B28" s="50" t="s">
+        <v>286</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>289</v>
+      </c>
+      <c r="E28" s="51">
+        <v>12459</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B29" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>290</v>
+      </c>
+      <c r="E29" s="52">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B30" s="50" t="s">
+        <v>272</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D30" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="E10" s="70">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B11" s="68" t="s">
-        <v>195</v>
-      </c>
-      <c r="C11" s="69" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="69" t="s">
-        <v>211</v>
-      </c>
-      <c r="E11" s="70">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B12" s="68" t="s">
-        <v>233</v>
-      </c>
-      <c r="C12" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D12" s="69" t="s">
-        <v>234</v>
-      </c>
-      <c r="E12" s="70">
-        <v>12441</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B13" s="68" t="s">
-        <v>232</v>
-      </c>
-      <c r="C13" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D13" s="69" t="s">
-        <v>235</v>
-      </c>
-      <c r="E13" s="70">
-        <v>31441</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B14" s="68" t="s">
-        <v>279</v>
-      </c>
-      <c r="C14" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D14" s="69" t="s">
-        <v>202</v>
-      </c>
-      <c r="E14" s="70">
-        <v>15500</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B15" s="68" t="s">
-        <v>280</v>
-      </c>
-      <c r="C15" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D15" s="69" t="s">
-        <v>203</v>
-      </c>
-      <c r="E15" s="70">
-        <v>14521</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B16" s="68" t="s">
-        <v>281</v>
-      </c>
-      <c r="C16" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D16" s="69" t="s">
-        <v>295</v>
-      </c>
-      <c r="E16" s="70">
-        <v>2564</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B17" s="68" t="s">
-        <v>282</v>
-      </c>
-      <c r="C17" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D17" s="69" t="s">
-        <v>296</v>
-      </c>
-      <c r="E17" s="70">
-        <v>2145</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B18" s="68" t="s">
-        <v>283</v>
-      </c>
-      <c r="C18" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D18" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="E18" s="70">
-        <v>10331</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B19" s="68" t="s">
-        <v>284</v>
-      </c>
-      <c r="C19" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D19" s="69" t="s">
-        <v>207</v>
-      </c>
-      <c r="E19" s="70">
-        <v>11922</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B20" s="68" t="s">
-        <v>285</v>
-      </c>
-      <c r="C20" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D20" s="69" t="s">
-        <v>208</v>
-      </c>
-      <c r="E20" s="70">
-        <v>453011</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B21" s="68" t="s">
-        <v>286</v>
-      </c>
-      <c r="C21" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D21" s="69" t="s">
-        <v>209</v>
-      </c>
-      <c r="E21" s="70">
-        <v>478221</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B22" s="68" t="s">
-        <v>287</v>
-      </c>
-      <c r="C22" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D22" s="69" t="s">
-        <v>300</v>
-      </c>
-      <c r="E22" s="70">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B23" s="68" t="s">
-        <v>288</v>
-      </c>
-      <c r="C23" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D23" s="69" t="s">
-        <v>301</v>
-      </c>
-      <c r="E23" s="69">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B24" s="68" t="s">
-        <v>289</v>
-      </c>
-      <c r="C24" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D24" s="69" t="s">
-        <v>204</v>
-      </c>
-      <c r="E24" s="69">
-        <v>4309</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B25" s="68" t="s">
-        <v>290</v>
-      </c>
-      <c r="C25" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D25" s="69" t="s">
-        <v>205</v>
-      </c>
-      <c r="E25" s="69">
-        <v>5612</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B26" s="68" t="s">
-        <v>306</v>
-      </c>
-      <c r="C26" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D26" s="69" t="s">
-        <v>310</v>
-      </c>
-      <c r="E26" s="69">
-        <v>7127</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B27" s="68" t="s">
-        <v>307</v>
-      </c>
-      <c r="C27" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D27" s="69" t="s">
-        <v>311</v>
-      </c>
-      <c r="E27" s="69">
-        <v>2727</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B28" s="68" t="s">
-        <v>305</v>
-      </c>
-      <c r="C28" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D28" s="69" t="s">
-        <v>308</v>
-      </c>
-      <c r="E28" s="69">
-        <v>12459</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B29" s="68" t="s">
-        <v>304</v>
-      </c>
-      <c r="C29" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D29" s="69" t="s">
-        <v>309</v>
-      </c>
-      <c r="E29" s="70">
-        <v>1557</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B30" s="68" t="s">
-        <v>291</v>
-      </c>
-      <c r="C30" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D30" s="69" t="s">
-        <v>212</v>
-      </c>
-      <c r="E30" s="70">
+      <c r="E30" s="52">
         <v>5002</v>
       </c>
     </row>
     <row r="31" spans="1:5" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A31"/>
-      <c r="B31" s="68" t="s">
-        <v>292</v>
-      </c>
-      <c r="C31" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D31" s="69" t="s">
-        <v>213</v>
-      </c>
-      <c r="E31" s="70">
+      <c r="B31" s="50" t="s">
+        <v>273</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="E31" s="52">
         <v>4291</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A32"/>
-      <c r="B32" s="68" t="s">
-        <v>192</v>
-      </c>
-      <c r="C32" s="69" t="s">
-        <v>201</v>
-      </c>
-      <c r="D32" s="69" t="s">
-        <v>303</v>
-      </c>
-      <c r="E32" s="70">
+      <c r="B32" s="50" t="s">
+        <v>190</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>284</v>
+      </c>
+      <c r="E32" s="52">
         <v>56217</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A33"/>
-      <c r="B33" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>201</v>
+      <c r="B33" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>199</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="E33" s="22">
         <v>57421</v>
@@ -2927,31 +3220,31 @@
     </row>
     <row r="34" spans="1:5" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A34"/>
-      <c r="B34" s="43" t="s">
-        <v>293</v>
-      </c>
-      <c r="C34" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="E34" s="36">
+      <c r="B34" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="E34" s="31">
         <v>2025</v>
       </c>
     </row>
     <row r="35" spans="1:5" s="1" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
-      <c r="B35" s="63" t="s">
-        <v>294</v>
-      </c>
-      <c r="C35" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="E35" s="42">
+      <c r="B35" s="45" t="s">
+        <v>275</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="E35" s="34">
         <v>2024</v>
       </c>
     </row>
@@ -2989,8 +3282,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5" ht="22" x14ac:dyDescent="0.2">
-      <c r="B2" s="83" t="s">
-        <v>319</v>
+      <c r="B2" s="64" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -2999,7 +3292,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>13</v>
@@ -3010,181 +3303,181 @@
     </row>
     <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A5"/>
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="73" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="73" t="s">
-        <v>315</v>
-      </c>
-      <c r="E5" s="74" t="s">
-        <v>17</v>
+      <c r="C5" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="48">
+        <v>12345678</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A6"/>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="76" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="76" t="s">
+      <c r="C6" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="77" t="s">
+      <c r="E6" s="58" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A7"/>
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="73" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="78" t="s">
+      <c r="C7" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="55" t="s">
         <v>18</v>
+      </c>
+      <c r="E7" s="59" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A8"/>
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="73" t="s">
-        <v>316</v>
-      </c>
-      <c r="E8" s="79">
+      <c r="C8" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>296</v>
+      </c>
+      <c r="E8" s="60">
         <v>45292</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A9"/>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="73" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="73" t="s">
-        <v>317</v>
-      </c>
-      <c r="E9" s="78" t="b">
+      <c r="C9" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>297</v>
+      </c>
+      <c r="E9" s="59" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10"/>
-      <c r="B10" s="72" t="s">
+      <c r="B10" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="73" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="73" t="s">
-        <v>318</v>
-      </c>
-      <c r="E10" s="78" t="b">
+      <c r="C10" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="E10" s="59" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11"/>
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="73" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="73" t="s">
-        <v>312</v>
-      </c>
-      <c r="E11" s="78" t="b">
+      <c r="C11" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="E11" s="59" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12"/>
-      <c r="B12" s="72" t="s">
+      <c r="B12" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="73" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="79">
+      <c r="C12" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="60">
         <v>45292</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13"/>
-      <c r="B13" s="72" t="s">
+      <c r="B13" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="73" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="73" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="78" t="b">
+      <c r="C13" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="59" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14"/>
-      <c r="B14" s="72" t="s">
+      <c r="B14" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="73" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="73" t="s">
-        <v>314</v>
-      </c>
-      <c r="E14" s="78" t="b">
+      <c r="C14" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="55" t="s">
+        <v>295</v>
+      </c>
+      <c r="E14" s="59" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15"/>
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="73" t="s">
-        <v>313</v>
-      </c>
-      <c r="E15" s="79">
+      <c r="C15" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="55" t="s">
+        <v>294</v>
+      </c>
+      <c r="E15" s="60">
         <v>45292</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
-      <c r="B16" s="80" t="s">
+      <c r="B16" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="81" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="81" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="82" t="b">
+      <c r="C16" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="63" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3196,15 +3489,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="E5" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15EF5264-368E-4981-A103-255E69D1470C}">
-  <dimension ref="B2:E75"/>
+  <dimension ref="B2:E72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -3215,8 +3505,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="87" t="s">
-        <v>328</v>
+      <c r="B2" s="65" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
@@ -3224,7 +3514,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>13</v>
@@ -3233,739 +3523,913 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="B4" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="C4" s="25" t="s">
+    <row r="4" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="114" t="s">
+        <v>280</v>
+      </c>
+      <c r="C4" s="115" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="115" t="s">
+        <v>322</v>
+      </c>
+      <c r="E4" s="96">
+        <v>100000000000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="102" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="116" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="85"/>
-      <c r="E4" s="86"/>
-    </row>
-    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B5" s="3" t="s">
+      <c r="E5" s="91" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C6" s="100" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="100" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="94" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="102" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="100" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="100" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="95">
+        <v>41961</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B8" s="102" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="100" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="100" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="95">
+        <v>41961</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B9" s="102" t="s">
+        <v>302</v>
+      </c>
+      <c r="C9" s="116" t="s">
+        <v>328</v>
+      </c>
+      <c r="D9" s="116" t="s">
+        <v>325</v>
+      </c>
+      <c r="E9" s="91" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="B10" s="102" t="s">
+        <v>303</v>
+      </c>
+      <c r="C10" s="116" t="s">
+        <v>328</v>
+      </c>
+      <c r="D10" s="116" t="s">
+        <v>327</v>
+      </c>
+      <c r="E10" s="117" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="102" t="s">
+        <v>304</v>
+      </c>
+      <c r="C11" s="116" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="116" t="s">
+        <v>330</v>
+      </c>
+      <c r="E11" s="91" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="102" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="116" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="116" t="s">
+        <v>331</v>
+      </c>
+      <c r="E12" s="91" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B13" s="102" t="s">
+        <v>305</v>
+      </c>
+      <c r="C13" s="116" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="116" t="s">
+        <v>332</v>
+      </c>
+      <c r="E13" s="91" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" s="102" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="100" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="100" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="94" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B15" s="102" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="100" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="100" t="s">
+        <v>318</v>
+      </c>
+      <c r="E15" s="94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B16" s="102" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="100" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="100" t="s">
+        <v>319</v>
+      </c>
+      <c r="E16" s="94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B17" s="102" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="100" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="100" t="s">
+        <v>321</v>
+      </c>
+      <c r="E17" s="94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B18" s="102" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="100" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="100" t="s">
+        <v>320</v>
+      </c>
+      <c r="E18" s="94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="104" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="112" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="113">
+        <v>12345678</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B20" s="82"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="84"/>
+    </row>
+    <row r="21" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="65" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B23" s="108" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="76" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="76" t="s">
+        <v>336</v>
+      </c>
+      <c r="E23" s="109" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B24" s="97" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="77" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="77" t="s">
+        <v>338</v>
+      </c>
+      <c r="E24" s="118">
+        <v>46024</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B25" s="97" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="77" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="77" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="119" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B26" s="97" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="77" t="s">
+        <v>339</v>
+      </c>
+      <c r="E26" s="110" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B27" s="97" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="77" t="s">
+        <v>340</v>
+      </c>
+      <c r="E27" s="110" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B28" s="97" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="77" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="77" t="s">
+        <v>337</v>
+      </c>
+      <c r="E28" s="118">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B29" s="97" t="s">
+        <v>280</v>
+      </c>
+      <c r="C29" s="116" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="116" t="s">
+        <v>322</v>
+      </c>
+      <c r="E29" s="120">
+        <v>100000000000</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="111" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="122" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="123">
+        <v>12345678</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="66" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B34" s="88" t="s">
+        <v>280</v>
+      </c>
+      <c r="C34" s="87" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="87" t="s">
+        <v>322</v>
+      </c>
+      <c r="E34" s="96">
+        <v>100000000000</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B35" s="89" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="90" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="E35" s="91" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="4" t="s">
+    </row>
+    <row r="36" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B36" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="93" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="93" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="94" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B6" s="3" t="s">
+    <row r="37" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B37" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C37" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D37" s="93" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="95">
+        <v>41961</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B38" s="92" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="93" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="27" t="s">
+      <c r="E38" s="95">
+        <v>41961</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B39" s="92" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="93" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="93" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="94" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B40" s="92" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="93" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="93" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="94" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B41" s="92" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D41" s="93" t="s">
+        <v>318</v>
+      </c>
+      <c r="E41" s="94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B42" s="92" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="93" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="93" t="s">
+        <v>319</v>
+      </c>
+      <c r="E42" s="94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B43" s="98" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="99" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="99" t="s">
+        <v>321</v>
+      </c>
+      <c r="E43" s="94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B44" s="98" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" s="99" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" s="99" t="s">
+        <v>320</v>
+      </c>
+      <c r="E44" s="94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B45" s="98" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="99" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="100" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="101">
+        <v>12345678</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B46" s="98" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" s="99" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" s="99" t="s">
+        <v>54</v>
+      </c>
+      <c r="E46" s="94" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B47" s="98" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" s="99" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" s="99" t="s">
+        <v>317</v>
+      </c>
+      <c r="E47" s="95">
+        <v>41961</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B48" s="98" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" s="99" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" s="99" t="s">
+        <v>59</v>
+      </c>
+      <c r="E48" s="94" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B49" s="98" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="99" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" s="99" t="s">
+        <v>60</v>
+      </c>
+      <c r="E49" s="94" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B50" s="102" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="103" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="103" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" s="91" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="104" t="s">
+        <v>40</v>
+      </c>
+      <c r="C51" s="105" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E51" s="107">
         <v>41961</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="28" t="s">
+    <row r="53" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="65" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B55" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E55" s="48">
+        <v>12345678</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B56" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="E56" s="124">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B57" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="C57" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E57" s="124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B58" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="E58" s="124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B59" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="C59" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D59" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="E59" s="124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B60" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="C60" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="E60" s="124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B61" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="6">
-        <v>41961</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="29"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="29"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B15" s="3" t="s">
+      <c r="C61" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D61" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="E61" s="124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B62" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C62" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D62" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="E62" s="124">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B63" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D63" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="E63" s="124">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B64" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D64" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="E64" s="124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B65" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D65" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="E65" s="124">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B66" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="E66" s="124">
+        <v>0.36599999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B67" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="E67" s="124">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B68" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="E68" s="124">
+        <v>0.52100000000000002</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B69" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="C69" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D69" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="E69" s="124">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B70" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E70" s="124">
         <v>1</v>
       </c>
-      <c r="C15" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="4">
-        <v>9284483</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" s="6">
-        <v>41961</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" s="31">
-        <v>41961</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="84" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B27" s="88" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="21"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B28" s="89" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="22"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B29" s="89" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="22"/>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B30" s="89" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="22"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B31" s="89" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="22"/>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B32" s="89" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="22"/>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B33" s="89" t="s">
-        <v>299</v>
-      </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="22"/>
-    </row>
-    <row r="34" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="90" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="24"/>
-    </row>
-    <row r="36" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="84" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B38" s="88" t="s">
-        <v>299</v>
-      </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="21"/>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B39" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="22"/>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B40" s="89" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="22"/>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B41" s="89" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="22"/>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B42" s="89" t="s">
-        <v>30</v>
-      </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="22"/>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B43" s="89" t="s">
-        <v>322</v>
-      </c>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="22"/>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B44" s="89" t="s">
-        <v>323</v>
-      </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="22"/>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B45" s="89" t="s">
-        <v>324</v>
-      </c>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="22"/>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B46" s="89" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="22"/>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B47" s="89" t="s">
-        <v>325</v>
-      </c>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="22"/>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B48" s="89" t="s">
-        <v>32</v>
-      </c>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="22"/>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B49" s="89" t="s">
-        <v>33</v>
-      </c>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="22"/>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B50" s="89" t="s">
-        <v>34</v>
-      </c>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="22"/>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B51" s="89" t="s">
-        <v>35</v>
-      </c>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="22"/>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B52" s="89" t="s">
-        <v>36</v>
-      </c>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="22"/>
-    </row>
-    <row r="53" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="90" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23"/>
-      <c r="E53" s="24"/>
-    </row>
-    <row r="56" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="84" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E57" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B58" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D58" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="E58" s="26">
-        <v>39285463</v>
-      </c>
-    </row>
-    <row r="59" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B59" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="C59" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D59" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="E59" s="22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B60" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="C60" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D60" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="E60" s="22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B61" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="C61" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D61" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="E61" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B62" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="C62" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D62" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="E62" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B63" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="C63" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D63" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="E63" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B64" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="C64" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D64" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="E64" s="22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B65" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D65" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="E65" s="22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B66" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C66" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D66" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="E66" s="22">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B67" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C67" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D67" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="E67" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B68" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C68" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="D68" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="E68" s="22">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="69" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B69" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C69" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="D69" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="E69" s="22">
-        <v>0.36599999999999999</v>
-      </c>
-    </row>
-    <row r="70" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B70" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="C70" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="D70" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="E70" s="22">
-        <v>0.54</v>
-      </c>
     </row>
     <row r="71" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B71" s="35" t="s">
-        <v>134</v>
+      <c r="B71" s="30" t="s">
+        <v>135</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="E71" s="22">
-        <v>0.52100000000000002</v>
-      </c>
-    </row>
-    <row r="72" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B72" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="C72" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="D72" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="E72" s="22">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="73" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B73" s="35" t="s">
+      <c r="E71" s="124">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="C73" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="D73" s="17" t="s">
+      <c r="C72" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="D72" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="E73" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B74" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="C74" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="D74" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="E74" s="22">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="C75" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="D75" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="E75" s="24">
+      <c r="E72" s="125">
         <v>0.25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="E35 E5" twoDigitTextYear="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -3985,8 +4449,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="84" t="s">
-        <v>330</v>
+      <c r="B2" s="65" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
@@ -3994,7 +4458,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>13</v>
@@ -4004,176 +4468,176 @@
       </c>
     </row>
     <row r="4" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="36">
+        <v>12345678</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="33">
+        <v>90924682245</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B8" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="26">
-        <v>39285463</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B5" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="38">
-        <v>90924682245</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B6" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="27" t="s">
+      <c r="D8" s="26" t="s">
         <v>80</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B8" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>82</v>
       </c>
       <c r="E8" s="6">
         <v>42471</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B9" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>83</v>
+      <c r="B9" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>81</v>
       </c>
       <c r="E9" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B10" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>84</v>
+      <c r="B10" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>82</v>
       </c>
       <c r="E10" s="6">
         <v>46617</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B11" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>85</v>
+      <c r="B11" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>83</v>
       </c>
       <c r="E11" s="6">
         <v>46098</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B12" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>86</v>
+      <c r="B12" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>84</v>
       </c>
       <c r="E12" s="4" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B13" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>87</v>
+      <c r="B13" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>85</v>
       </c>
       <c r="E13" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B14" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="27" t="s">
-        <v>88</v>
+      <c r="B14" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>86</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>89</v>
+      <c r="B15" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>87</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="84" t="s">
-        <v>331</v>
+      <c r="B18" s="65" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
@@ -4181,7 +4645,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>13</v>
@@ -4191,162 +4655,162 @@
       </c>
     </row>
     <row r="20" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="144" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="145" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="146">
+        <v>12345678</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B21" s="80" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="81" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="78" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B22" s="80" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="81" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="78" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B23" s="141" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="81" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="78" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B24" s="80" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="26">
-        <v>39285463</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B21" s="3" t="s">
+      <c r="D24" s="81" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" s="79">
+        <v>41961</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B25" s="80" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="81" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" s="79">
+        <v>41961</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B26" s="80" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="81" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="81" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" s="78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="B27" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C27" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="81" t="s">
+        <v>108</v>
+      </c>
+      <c r="E27" s="142" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="B28" s="141" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="81" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" s="81" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="142" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B29" s="80" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B22" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="27" t="s">
+      <c r="D29" s="81" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29" s="79">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="143" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B23" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="E23" s="41" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B24" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="6">
-        <v>41961</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B25" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="E25" s="6">
-        <v>41961</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B26" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="E26" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="B27" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" s="93" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="B28" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="E28" s="93" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B29" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="E29" s="6">
-        <v>46332</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="E30" s="31">
+      <c r="D30" s="85" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" s="86">
         <v>46345</v>
       </c>
     </row>
     <row r="33" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="84" t="s">
-        <v>333</v>
+      <c r="B33" s="65" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="34" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
@@ -4354,7 +4818,7 @@
         <v>12</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D34" s="15" t="s">
         <v>13</v>
@@ -4364,218 +4828,218 @@
       </c>
     </row>
     <row r="35" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B35" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="C35" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>124</v>
+      <c r="B35" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B36" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="C36" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="27" t="s">
-        <v>175</v>
+      <c r="B36" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>173</v>
       </c>
       <c r="E36" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="37" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B37" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="C37" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>176</v>
+      <c r="B37" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C37" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>174</v>
       </c>
       <c r="E37" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="38" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B38" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="C38" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D38" s="27" t="s">
-        <v>177</v>
+      <c r="B38" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>175</v>
       </c>
       <c r="E38" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="39" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B39" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="C39" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D39" s="27" t="s">
-        <v>178</v>
+      <c r="B39" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="C39" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>176</v>
       </c>
       <c r="E39" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="40" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B40" s="35" t="s">
-        <v>165</v>
-      </c>
-      <c r="C40" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D40" s="27" t="s">
-        <v>179</v>
+      <c r="B40" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>177</v>
       </c>
       <c r="E40" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="41" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B41" s="92" t="s">
-        <v>332</v>
-      </c>
-      <c r="C41" s="91" t="s">
-        <v>42</v>
-      </c>
-      <c r="D41" s="91" t="s">
-        <v>335</v>
+      <c r="B41" s="68" t="s">
+        <v>312</v>
+      </c>
+      <c r="C41" s="67" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" s="67" t="s">
+        <v>315</v>
       </c>
       <c r="E41" s="4">
         <v>9</v>
       </c>
     </row>
     <row r="42" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B42" s="35" t="s">
-        <v>166</v>
-      </c>
-      <c r="C42" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D42" s="27" t="s">
-        <v>180</v>
+      <c r="B42" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="C42" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" s="26" t="s">
+        <v>178</v>
       </c>
       <c r="E42" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="43" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B43" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="C43" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D43" s="27" t="s">
-        <v>181</v>
+      <c r="B43" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="C43" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" s="26" t="s">
+        <v>179</v>
       </c>
       <c r="E43" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="44" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B44" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="C44" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D44" s="27" t="s">
-        <v>182</v>
+      <c r="B44" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="C44" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>180</v>
       </c>
       <c r="E44" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="45" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B45" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="C45" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D45" s="27" t="s">
-        <v>183</v>
+      <c r="B45" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C45" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>181</v>
       </c>
       <c r="E45" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B46" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="C46" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D46" s="27" t="s">
-        <v>184</v>
+      <c r="B46" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>182</v>
       </c>
       <c r="E46" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B47" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="C47" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D47" s="27" t="s">
-        <v>185</v>
+      <c r="B47" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="C47" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>183</v>
       </c>
       <c r="E47" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="48" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B48" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="C48" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D48" s="27" t="s">
-        <v>186</v>
+      <c r="B48" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="C48" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>184</v>
       </c>
       <c r="E48" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="49" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="C49" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="D49" s="30" t="s">
-        <v>187</v>
+      <c r="B49" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D49" s="27" t="s">
+        <v>185</v>
       </c>
       <c r="E49" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="51" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="84" t="s">
-        <v>334</v>
+      <c r="B51" s="65" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
@@ -4583,7 +5047,7 @@
         <v>12</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D52" s="15" t="s">
         <v>13</v>
@@ -4593,81 +5057,81 @@
       </c>
     </row>
     <row r="53" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B53" s="33" t="s">
+      <c r="B53" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B54" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D54" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B55" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E55" s="22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B56" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="C53" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D53" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="E53" s="21" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B54" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="C54" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D54" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="E54" s="22" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B55" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="C55" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D55" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="E55" s="22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B56" s="35" t="s">
-        <v>118</v>
-      </c>
       <c r="C56" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D56" s="27" t="s">
-        <v>80</v>
+        <v>20</v>
+      </c>
+      <c r="D56" s="26" t="s">
+        <v>78</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B57" s="35" t="s">
+      <c r="B57" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E57" s="4">
-        <v>39285463</v>
+      <c r="C57" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E57" s="48">
+        <v>12345678</v>
       </c>
     </row>
     <row r="58" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B58" s="35" t="s">
+      <c r="B58" s="30" t="s">
         <v>0</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>15</v>
@@ -4677,98 +5141,98 @@
       </c>
     </row>
     <row r="59" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B59" s="35" t="s">
+      <c r="B59" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B60" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C60" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B60" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="C60" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D60" s="27" t="s">
-        <v>82</v>
+      <c r="D60" s="26" t="s">
+        <v>80</v>
       </c>
       <c r="E60" s="6">
         <v>42471</v>
       </c>
     </row>
     <row r="61" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B61" s="35" t="s">
-        <v>117</v>
+      <c r="B61" s="30" t="s">
+        <v>115</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D61" s="27" t="s">
-        <v>125</v>
+        <v>22</v>
+      </c>
+      <c r="D61" s="26" t="s">
+        <v>123</v>
       </c>
       <c r="E61" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B62" s="35" t="s">
-        <v>121</v>
+      <c r="B62" s="30" t="s">
+        <v>119</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D62" s="27" t="s">
-        <v>126</v>
+        <v>21</v>
+      </c>
+      <c r="D62" s="26" t="s">
+        <v>124</v>
       </c>
       <c r="E62" s="6">
         <v>46332</v>
       </c>
     </row>
     <row r="63" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B63" s="35" t="s">
-        <v>122</v>
+      <c r="B63" s="30" t="s">
+        <v>120</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D63" s="27" t="s">
-        <v>127</v>
+        <v>21</v>
+      </c>
+      <c r="D63" s="26" t="s">
+        <v>125</v>
       </c>
       <c r="E63" s="6">
         <v>46345</v>
       </c>
     </row>
     <row r="64" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B64" s="35" t="s">
-        <v>72</v>
+      <c r="B64" s="30" t="s">
+        <v>70</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D64" s="27" t="s">
-        <v>85</v>
+        <v>21</v>
+      </c>
+      <c r="D64" s="26" t="s">
+        <v>83</v>
       </c>
       <c r="E64" s="6">
         <v>46098</v>
       </c>
     </row>
     <row r="65" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C65" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="D65" s="30" t="s">
-        <v>86</v>
+      <c r="B65" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D65" s="27" t="s">
+        <v>84</v>
       </c>
       <c r="E65" s="9" t="b">
         <v>1</v>
@@ -4791,8 +5255,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="84" t="s">
-        <v>336</v>
+      <c r="B2" s="65" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
@@ -4800,7 +5264,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>13</v>
@@ -4813,25 +5277,25 @@
       <c r="B4" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="44" t="s">
-        <v>17</v>
+      <c r="C4" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="36">
+        <v>12345678</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="E5" s="4">
         <v>5</v>
@@ -4839,13 +5303,13 @@
     </row>
     <row r="6" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="E6" s="4">
         <v>1</v>
@@ -4853,13 +5317,13 @@
     </row>
     <row r="7" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="E7" s="4">
         <v>2</v>
@@ -4867,13 +5331,13 @@
     </row>
     <row r="8" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="E8" s="4">
         <v>4</v>
@@ -4881,13 +5345,13 @@
     </row>
     <row r="9" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="E9" s="4">
         <v>0</v>
@@ -4895,13 +5359,13 @@
     </row>
     <row r="10" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="E10" s="4">
         <v>0</v>
@@ -4909,13 +5373,13 @@
     </row>
     <row r="11" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="E11" s="4">
         <v>3</v>
@@ -4923,13 +5387,13 @@
     </row>
     <row r="12" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="E12" s="4">
         <v>3</v>
@@ -4937,13 +5401,13 @@
     </row>
     <row r="13" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="E13" s="4">
         <v>7</v>
@@ -4951,21 +5415,21 @@
     </row>
     <row r="14" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="E14" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="84" t="s">
-        <v>320</v>
+      <c r="B16" s="65" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
@@ -4973,7 +5437,7 @@
         <v>12</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>13</v>
@@ -4983,78 +5447,78 @@
       </c>
     </row>
     <row r="18" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B18" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="C18" s="25" t="s">
+      <c r="B18" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="25" t="s">
-        <v>262</v>
-      </c>
-      <c r="E18" s="44" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B19" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="27" t="s">
-        <v>261</v>
+      <c r="D19" s="26" t="s">
+        <v>247</v>
       </c>
       <c r="E19" s="6">
         <v>46136</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B20" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>265</v>
+      <c r="B20" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>251</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B21" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="27" t="s">
-        <v>266</v>
+      <c r="B21" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>252</v>
       </c>
       <c r="E21" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="37" t="s">
+      <c r="B22" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="58" t="s">
-        <v>17</v>
+      <c r="C22" s="73" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="74" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="75">
+        <v>12345678</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="84" t="s">
-        <v>321</v>
+      <c r="B24" s="65" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="20" thickBot="1" x14ac:dyDescent="0.25">
@@ -5062,7 +5526,7 @@
         <v>12</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>13</v>
@@ -5072,87 +5536,87 @@
       </c>
     </row>
     <row r="26" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B26" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="C26" s="25" t="s">
+      <c r="B26" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="B27" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="25" t="s">
-        <v>269</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B27" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="27" t="s">
-        <v>268</v>
+      <c r="D27" s="26" t="s">
+        <v>254</v>
       </c>
       <c r="E27" s="6">
         <v>45333</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B28" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="C28" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>267</v>
+      <c r="B28" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>253</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B29" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="C29" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>265</v>
+      <c r="B29" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>251</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="B30" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="C30" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="27" t="s">
-        <v>266</v>
+      <c r="B30" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>252</v>
       </c>
       <c r="E30" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="31" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="37" t="s">
+      <c r="B31" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" s="58" t="s">
-        <v>17</v>
+      <c r="C31" s="73" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="74" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" s="75">
+        <v>12345678</v>
       </c>
     </row>
   </sheetData>
@@ -5161,12 +5625,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d400e6ca-83e7-4ec8-8dba-73297945a25b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="62c0568a-750b-4e53-9e60-20dd32e5e402">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5399,20 +5865,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d400e6ca-83e7-4ec8-8dba-73297945a25b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="62c0568a-750b-4e53-9e60-20dd32e5e402">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF42BF03-D490-44FF-857F-8695E90A9225}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{914EDA56-117D-4F3A-B12C-F495439EC5A7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d400e6ca-83e7-4ec8-8dba-73297945a25b"/>
+    <ds:schemaRef ds:uri="62c0568a-750b-4e53-9e60-20dd32e5e402"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5437,12 +5904,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{914EDA56-117D-4F3A-B12C-F495439EC5A7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF42BF03-D490-44FF-857F-8695E90A9225}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d400e6ca-83e7-4ec8-8dba-73297945a25b"/>
-    <ds:schemaRef ds:uri="62c0568a-750b-4e53-9e60-20dd32e5e402"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>